--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/4.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/4.xlsx
@@ -426,13 +426,13 @@
         <v>-16.88508278957571</v>
       </c>
       <c r="E2">
-        <v>-20.73569889039586</v>
+        <v>-18.60267894940693</v>
       </c>
       <c r="F2">
-        <v>-2.044152446727014</v>
+        <v>-1.363333017346754</v>
       </c>
       <c r="G2">
-        <v>-13.60685976217704</v>
+        <v>-12.37992192714005</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.60657721810962</v>
       </c>
       <c r="E3">
-        <v>-21.45033737354631</v>
+        <v>-17.97197120351463</v>
       </c>
       <c r="F3">
-        <v>-2.113974706741581</v>
+        <v>-1.041063306226828</v>
       </c>
       <c r="G3">
-        <v>-13.7579133340429</v>
+        <v>-11.88315470569917</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.17110683366806</v>
       </c>
       <c r="E4">
-        <v>-21.95946012080667</v>
+        <v>-18.42150376130806</v>
       </c>
       <c r="F4">
-        <v>-1.746758608713158</v>
+        <v>-1.156378675635742</v>
       </c>
       <c r="G4">
-        <v>-13.29649611787037</v>
+        <v>-11.31772676977381</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.60233451873759</v>
       </c>
       <c r="E5">
-        <v>-22.17299578416436</v>
+        <v>-19.75011275041846</v>
       </c>
       <c r="F5">
-        <v>-1.841952105540669</v>
+        <v>-1.202918841427227</v>
       </c>
       <c r="G5">
-        <v>-13.42434938659702</v>
+        <v>-11.64815232004847</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.92269390836079</v>
       </c>
       <c r="E6">
-        <v>-22.56260757388828</v>
+        <v>-19.19955446598792</v>
       </c>
       <c r="F6">
-        <v>-1.919058200128053</v>
+        <v>-0.9353926184887095</v>
       </c>
       <c r="G6">
-        <v>-13.78382497397878</v>
+        <v>-11.05063195566541</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.14645554695924</v>
       </c>
       <c r="E7">
-        <v>-22.95583761434434</v>
+        <v>-20.30387266597242</v>
       </c>
       <c r="F7">
-        <v>-1.466139210605992</v>
+        <v>-1.1222789314995</v>
       </c>
       <c r="G7">
-        <v>-13.03280785512188</v>
+        <v>-11.77963394668616</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.31042279152792</v>
       </c>
       <c r="E8">
-        <v>-23.12724035553466</v>
+        <v>-20.90160859261487</v>
       </c>
       <c r="F8">
-        <v>-1.44223004225899</v>
+        <v>-1.097002956937879</v>
       </c>
       <c r="G8">
-        <v>-13.0749345471091</v>
+        <v>-11.0165068522466</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.44312917814128</v>
       </c>
       <c r="E9">
-        <v>-23.83474196364903</v>
+        <v>-21.30512732601635</v>
       </c>
       <c r="F9">
-        <v>-1.716487578712656</v>
+        <v>-0.6198053472071678</v>
       </c>
       <c r="G9">
-        <v>-12.72665191419562</v>
+        <v>-11.11267820016243</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.55169606321243</v>
       </c>
       <c r="E10">
-        <v>-23.8423407430339</v>
+        <v>-22.25257012942714</v>
       </c>
       <c r="F10">
-        <v>-1.518437358214336</v>
+        <v>-1.0427415785849</v>
       </c>
       <c r="G10">
-        <v>-13.16502773341483</v>
+        <v>-10.52451343747335</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.66445588012997</v>
       </c>
       <c r="E11">
-        <v>-24.98912244378833</v>
+        <v>-22.66856480871975</v>
       </c>
       <c r="F11">
-        <v>-1.526329214460807</v>
+        <v>-0.8478623485044969</v>
       </c>
       <c r="G11">
-        <v>-12.32989958404166</v>
+        <v>-10.06687686430666</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.788257116140079</v>
       </c>
       <c r="E12">
-        <v>-25.8280448960793</v>
+        <v>-23.40019412634699</v>
       </c>
       <c r="F12">
-        <v>-1.263172629572057</v>
+        <v>-0.6412153310999239</v>
       </c>
       <c r="G12">
-        <v>-11.75341773656067</v>
+        <v>-9.725059726831374</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.914044702080185</v>
       </c>
       <c r="E13">
-        <v>-26.0939568898097</v>
+        <v>-24.55315719412189</v>
       </c>
       <c r="F13">
-        <v>-1.335388043013312</v>
+        <v>-0.5174033972404958</v>
       </c>
       <c r="G13">
-        <v>-12.11186043373418</v>
+        <v>-9.77054331199542</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.056974613511272</v>
       </c>
       <c r="E14">
-        <v>-26.11547166982015</v>
+        <v>-24.92411167093421</v>
       </c>
       <c r="F14">
-        <v>-1.150113732968369</v>
+        <v>-0.3215127305612743</v>
       </c>
       <c r="G14">
-        <v>-11.58936365236209</v>
+        <v>-8.825468634717517</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.210230705860065</v>
       </c>
       <c r="E15">
-        <v>-28.18372537555137</v>
+        <v>-26.23175835386311</v>
       </c>
       <c r="F15">
-        <v>-1.167872273349585</v>
+        <v>-0.380612602914005</v>
       </c>
       <c r="G15">
-        <v>-10.91714744897646</v>
+        <v>-8.62400538592517</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.36588811284064</v>
       </c>
       <c r="E16">
-        <v>-27.63131041677768</v>
+        <v>-26.97493528020991</v>
       </c>
       <c r="F16">
-        <v>-0.7715788227480933</v>
+        <v>0.00705091608512164</v>
       </c>
       <c r="G16">
-        <v>-10.81534486309833</v>
+        <v>-8.117584613691777</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.535232793593372</v>
       </c>
       <c r="E17">
-        <v>-29.07169572981942</v>
+        <v>-27.56941070556684</v>
       </c>
       <c r="F17">
-        <v>-0.7924164047655148</v>
+        <v>0.07344207831729362</v>
       </c>
       <c r="G17">
-        <v>-10.53734511198357</v>
+        <v>-7.991485934100937</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.715658667628443</v>
       </c>
       <c r="E18">
-        <v>-29.7566500658496</v>
+        <v>-27.88408077893783</v>
       </c>
       <c r="F18">
-        <v>-0.5201303827305117</v>
+        <v>0.4751108049955515</v>
       </c>
       <c r="G18">
-        <v>-9.566607085685236</v>
+        <v>-8.2997242081714</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.911661275701107</v>
       </c>
       <c r="E19">
-        <v>-30.65818546400762</v>
+        <v>-28.74412856247458</v>
       </c>
       <c r="F19">
-        <v>-0.1842174604864786</v>
+        <v>0.2686352596433579</v>
       </c>
       <c r="G19">
-        <v>-9.30717618450025</v>
+        <v>-7.45461145345179</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.137805406029027</v>
       </c>
       <c r="E20">
-        <v>-30.96154567354446</v>
+        <v>-30.19990615866839</v>
       </c>
       <c r="F20">
-        <v>-0.2520193324056181</v>
+        <v>0.6957381790571718</v>
       </c>
       <c r="G20">
-        <v>-8.66197734326061</v>
+        <v>-6.923311931490774</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.39689990354613</v>
       </c>
       <c r="E21">
-        <v>-32.2503810754455</v>
+        <v>-29.64237628850304</v>
       </c>
       <c r="F21">
-        <v>0.1337016650339437</v>
+        <v>0.9252357112679692</v>
       </c>
       <c r="G21">
-        <v>-9.356526486854165</v>
+        <v>-6.01149168415485</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.699001833322662</v>
       </c>
       <c r="E22">
-        <v>-31.88006964194226</v>
+        <v>-30.79845268215821</v>
       </c>
       <c r="F22">
-        <v>-0.007639351436124793</v>
+        <v>0.8704657153296715</v>
       </c>
       <c r="G22">
-        <v>-8.719984722199719</v>
+        <v>-6.367656725997342</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.054532729109465</v>
       </c>
       <c r="E23">
-        <v>-32.67222427891902</v>
+        <v>-31.12396392230356</v>
       </c>
       <c r="F23">
-        <v>0.3556420014290012</v>
+        <v>0.7296316597101163</v>
       </c>
       <c r="G23">
-        <v>-8.6159574497192</v>
+        <v>-5.858220046777673</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.4639609691974907</v>
       </c>
       <c r="E24">
-        <v>-33.28122252041854</v>
+        <v>-31.52008765765052</v>
       </c>
       <c r="F24">
-        <v>0.2623446375864985</v>
+        <v>1.100536477783206</v>
       </c>
       <c r="G24">
-        <v>-8.347614559942496</v>
+        <v>-5.508686027650343</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.06609000901977045</v>
       </c>
       <c r="E25">
-        <v>-33.25013228211888</v>
+        <v>-31.577046803719</v>
       </c>
       <c r="F25">
-        <v>0.3676914336701228</v>
+        <v>1.302770782033066</v>
       </c>
       <c r="G25">
-        <v>-8.841233452575526</v>
+        <v>-6.484671268628421</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.5310493142262354</v>
       </c>
       <c r="E26">
-        <v>-33.06670644243819</v>
+        <v>-30.70460005834924</v>
       </c>
       <c r="F26">
-        <v>0.4309116054843783</v>
+        <v>1.063992221441303</v>
       </c>
       <c r="G26">
-        <v>-8.687597655189029</v>
+        <v>-5.87118083256392</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.9313419403078586</v>
       </c>
       <c r="E27">
-        <v>-33.69870706765968</v>
+        <v>-32.09011385184003</v>
       </c>
       <c r="F27">
-        <v>0.6161453255265841</v>
+        <v>1.413263396422881</v>
       </c>
       <c r="G27">
-        <v>-8.655664132917218</v>
+        <v>-6.355606340234394</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.260640325365112</v>
       </c>
       <c r="E28">
-        <v>-33.56895723039191</v>
+        <v>-32.81782603945064</v>
       </c>
       <c r="F28">
-        <v>0.1775189871724263</v>
+        <v>1.163502340804802</v>
       </c>
       <c r="G28">
-        <v>-8.363571389441784</v>
+        <v>-6.350607416470095</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.514374017486267</v>
       </c>
       <c r="E29">
-        <v>-34.38994918984951</v>
+        <v>-31.34191031934472</v>
       </c>
       <c r="F29">
-        <v>0.4708761908324404</v>
+        <v>1.352668320908097</v>
       </c>
       <c r="G29">
-        <v>-8.463907403646015</v>
+        <v>-5.711413904838692</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.690489885949121</v>
       </c>
       <c r="E30">
-        <v>-33.27353317155352</v>
+        <v>-32.356951918505</v>
       </c>
       <c r="F30">
-        <v>0.7529236943420329</v>
+        <v>1.128657894373444</v>
       </c>
       <c r="G30">
-        <v>-8.905441483309691</v>
+        <v>-5.646348442809857</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.783060703846598</v>
       </c>
       <c r="E31">
-        <v>-33.34550647319443</v>
+        <v>-31.58394366963268</v>
       </c>
       <c r="F31">
-        <v>0.5105019739127575</v>
+        <v>1.049847019671099</v>
       </c>
       <c r="G31">
-        <v>-8.627888655842733</v>
+        <v>-6.292103455700095</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.788720167771355</v>
       </c>
       <c r="E32">
-        <v>-32.91747963846343</v>
+        <v>-30.97364575609295</v>
       </c>
       <c r="F32">
-        <v>0.4564741951673682</v>
+        <v>0.9565678799114578</v>
       </c>
       <c r="G32">
-        <v>-8.159913248956899</v>
+        <v>-6.270932516976456</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.708486801243749</v>
       </c>
       <c r="E33">
-        <v>-32.91159715072747</v>
+        <v>-30.85227585997638</v>
       </c>
       <c r="F33">
-        <v>0.1871272206774978</v>
+        <v>1.010801093772741</v>
       </c>
       <c r="G33">
-        <v>-8.84190218277446</v>
+        <v>-6.399947787187393</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.543178634337856</v>
       </c>
       <c r="E34">
-        <v>-32.07821075791087</v>
+        <v>-30.1872219029729</v>
       </c>
       <c r="F34">
-        <v>0.3896009231067669</v>
+        <v>0.865270194979313</v>
       </c>
       <c r="G34">
-        <v>-8.533389133424238</v>
+        <v>-6.593896097605596</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.295322722740261</v>
       </c>
       <c r="E35">
-        <v>-31.5235564687404</v>
+        <v>-29.61834594118134</v>
       </c>
       <c r="F35">
-        <v>0.5074477832986358</v>
+        <v>1.105390710763611</v>
       </c>
       <c r="G35">
-        <v>-8.616305057000824</v>
+        <v>-6.8628713015803</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.9728032259461926</v>
       </c>
       <c r="E36">
-        <v>-31.36788564625272</v>
+        <v>-29.58090678232292</v>
       </c>
       <c r="F36">
-        <v>0.3910596781030968</v>
+        <v>1.128841791936865</v>
       </c>
       <c r="G36">
-        <v>-9.079039870297994</v>
+        <v>-6.408561826680576</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.5844899128461321</v>
       </c>
       <c r="E37">
-        <v>-31.44433534445021</v>
+        <v>-28.9794642997052</v>
       </c>
       <c r="F37">
-        <v>0.1477085294478805</v>
+        <v>0.9373282186140365</v>
       </c>
       <c r="G37">
-        <v>-9.131846382194908</v>
+        <v>-7.01908601394189</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.1396585179021992</v>
       </c>
       <c r="E38">
-        <v>-31.17773955114465</v>
+        <v>-28.26855727913706</v>
       </c>
       <c r="F38">
-        <v>0.2812645490664392</v>
+        <v>0.8256642927166631</v>
       </c>
       <c r="G38">
-        <v>-9.315978925089171</v>
+        <v>-6.68045362127538</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.3476260791840502</v>
       </c>
       <c r="E39">
-        <v>-30.08690035404398</v>
+        <v>-27.0524446413252</v>
       </c>
       <c r="F39">
-        <v>0.5606861279091572</v>
+        <v>1.250461037281083</v>
       </c>
       <c r="G39">
-        <v>-9.321987565242949</v>
+        <v>-7.657931918291669</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.8666446626996439</v>
       </c>
       <c r="E40">
-        <v>-29.1376303113711</v>
+        <v>-27.2678777352921</v>
       </c>
       <c r="F40">
-        <v>0.5596274743683795</v>
+        <v>1.284357831403639</v>
       </c>
       <c r="G40">
-        <v>-9.559638387325069</v>
+        <v>-7.138662918820366</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.409687622202018</v>
       </c>
       <c r="E41">
-        <v>-28.95211231669887</v>
+        <v>-26.53419249046538</v>
       </c>
       <c r="F41">
-        <v>0.6106110029084806</v>
+        <v>1.439067041020086</v>
       </c>
       <c r="G41">
-        <v>-8.762429226558716</v>
+        <v>-6.71133770061124</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.963421004729038</v>
       </c>
       <c r="E42">
-        <v>-28.88885859175973</v>
+        <v>-25.89899249835747</v>
       </c>
       <c r="F42">
-        <v>0.4145438939724628</v>
+        <v>1.523585367127719</v>
       </c>
       <c r="G42">
-        <v>-9.527585685413847</v>
+        <v>-6.204148881812737</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.522383391678341</v>
       </c>
       <c r="E43">
-        <v>-28.36595116962002</v>
+        <v>-25.31147280907633</v>
       </c>
       <c r="F43">
-        <v>0.3460958954791397</v>
+        <v>1.441076660339277</v>
       </c>
       <c r="G43">
-        <v>-9.32652301263175</v>
+        <v>-7.265453502428913</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.082230988139344</v>
       </c>
       <c r="E44">
-        <v>-27.89559215986533</v>
+        <v>-25.02448529731423</v>
       </c>
       <c r="F44">
-        <v>0.6778098233583821</v>
+        <v>1.590610230423033</v>
       </c>
       <c r="G44">
-        <v>-9.265850644533527</v>
+        <v>-7.246186127390354</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.630544870428625</v>
       </c>
       <c r="E45">
-        <v>-27.45183340643169</v>
+        <v>-24.03733230533018</v>
       </c>
       <c r="F45">
-        <v>0.680727333351042</v>
+        <v>1.630267491464656</v>
       </c>
       <c r="G45">
-        <v>-9.241604209003905</v>
+        <v>-7.023846578427362</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.165118322696527</v>
       </c>
       <c r="E46">
-        <v>-25.38959351418265</v>
+        <v>-24.42271450033094</v>
       </c>
       <c r="F46">
-        <v>0.6487846579316903</v>
+        <v>1.675348902259811</v>
       </c>
       <c r="G46">
-        <v>-9.367219548946011</v>
+        <v>-7.500978954274822</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.681646164955838</v>
       </c>
       <c r="E47">
-        <v>-26.08952351375619</v>
+        <v>-22.83836899858537</v>
       </c>
       <c r="F47">
-        <v>0.6595584043725006</v>
+        <v>1.70211842324868</v>
       </c>
       <c r="G47">
-        <v>-9.478808107438224</v>
+        <v>-6.755450719922029</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.169844835631259</v>
       </c>
       <c r="E48">
-        <v>-24.49257979732128</v>
+        <v>-22.64530656621636</v>
       </c>
       <c r="F48">
-        <v>0.7800427863748831</v>
+        <v>1.729492652441593</v>
       </c>
       <c r="G48">
-        <v>-9.731667575727759</v>
+        <v>-7.178717209300007</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.632021571397905</v>
       </c>
       <c r="E49">
-        <v>-24.77147492603168</v>
+        <v>-21.54498248030662</v>
       </c>
       <c r="F49">
-        <v>0.764562256351366</v>
+        <v>1.544697138755468</v>
       </c>
       <c r="G49">
-        <v>-9.732273405561445</v>
+        <v>-7.2236313806313</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.067107421030989</v>
       </c>
       <c r="E50">
-        <v>-23.94687150855296</v>
+        <v>-21.23656170106622</v>
       </c>
       <c r="F50">
-        <v>0.6621238582189707</v>
+        <v>1.6243032461645</v>
       </c>
       <c r="G50">
-        <v>-9.428633479245031</v>
+        <v>-6.771268506508667</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.471080030886223</v>
       </c>
       <c r="E51">
-        <v>-23.41458561674337</v>
+        <v>-20.85186783411462</v>
       </c>
       <c r="F51">
-        <v>0.8897053766270928</v>
+        <v>2.029721163707829</v>
       </c>
       <c r="G51">
-        <v>-10.02870627423887</v>
+        <v>-7.624515271618265</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.851996520731142</v>
       </c>
       <c r="E52">
-        <v>-23.14027330372874</v>
+        <v>-20.47043899692256</v>
       </c>
       <c r="F52">
-        <v>1.059426260317072</v>
+        <v>1.457635724721239</v>
       </c>
       <c r="G52">
-        <v>-9.644255931308843</v>
+        <v>-6.983322190481143</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.210128766081908</v>
       </c>
       <c r="E53">
-        <v>-23.32226361714899</v>
+        <v>-19.51983984712842</v>
       </c>
       <c r="F53">
-        <v>0.8996159642341861</v>
+        <v>1.833575359868545</v>
       </c>
       <c r="G53">
-        <v>-9.821343633295536</v>
+        <v>-7.697966345498076</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.544861902321293</v>
       </c>
       <c r="E54">
-        <v>-22.06439844898641</v>
+        <v>-19.28098095711984</v>
       </c>
       <c r="F54">
-        <v>0.8103013908643435</v>
+        <v>1.705508102660936</v>
       </c>
       <c r="G54">
-        <v>-9.819804229619775</v>
+        <v>-7.962045252620198</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.864256651578147</v>
       </c>
       <c r="E55">
-        <v>-22.06738271335747</v>
+        <v>-19.77927612302786</v>
       </c>
       <c r="F55">
-        <v>0.8767347998340582</v>
+        <v>1.669585121871132</v>
       </c>
       <c r="G55">
-        <v>-9.874117039737058</v>
+        <v>-7.6746005150819</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.164585819650187</v>
       </c>
       <c r="E56">
-        <v>-21.46156798908534</v>
+        <v>-18.66293029607899</v>
       </c>
       <c r="F56">
-        <v>0.812852762464966</v>
+        <v>1.757360588606574</v>
       </c>
       <c r="G56">
-        <v>-9.552974259154517</v>
+        <v>-7.168275748669146</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.445422317498537</v>
       </c>
       <c r="E57">
-        <v>-20.810762875547</v>
+        <v>-19.18636302120358</v>
       </c>
       <c r="F57">
-        <v>0.6926417417055073</v>
+        <v>2.025021007064344</v>
       </c>
       <c r="G57">
-        <v>-9.893076534040464</v>
+        <v>-7.805724602801352</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.710671069712106</v>
       </c>
       <c r="E58">
-        <v>-20.56435954784164</v>
+        <v>-18.06679744923525</v>
       </c>
       <c r="F58">
-        <v>0.7374812692190446</v>
+        <v>1.492740278517077</v>
       </c>
       <c r="G58">
-        <v>-9.848066356888534</v>
+        <v>-8.437585256063269</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.95011876709237</v>
       </c>
       <c r="E59">
-        <v>-20.12329976491657</v>
+        <v>-17.08316308155517</v>
       </c>
       <c r="F59">
-        <v>0.9008833663604694</v>
+        <v>1.569513369408535</v>
       </c>
       <c r="G59">
-        <v>-10.33035987323172</v>
+        <v>-8.322424618934182</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.161882160344126</v>
       </c>
       <c r="E60">
-        <v>-20.40205903940673</v>
+        <v>-17.09414010254976</v>
       </c>
       <c r="F60">
-        <v>0.6393802028077075</v>
+        <v>1.663587741874864</v>
       </c>
       <c r="G60">
-        <v>-10.39278351992021</v>
+        <v>-8.224929052802645</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.343335465467554</v>
       </c>
       <c r="E61">
-        <v>-19.52349885412662</v>
+        <v>-16.71498455930954</v>
       </c>
       <c r="F61">
-        <v>0.5878507801491614</v>
+        <v>1.415027818990844</v>
       </c>
       <c r="G61">
-        <v>-10.13036981720435</v>
+        <v>-8.164756577080851</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.479486263057623</v>
       </c>
       <c r="E62">
-        <v>-18.88087669312014</v>
+        <v>-16.67097232042899</v>
       </c>
       <c r="F62">
-        <v>0.5651518565776493</v>
+        <v>1.277371380728428</v>
       </c>
       <c r="G62">
-        <v>-10.11780298633727</v>
+        <v>-8.179418983274283</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.571817769186119</v>
       </c>
       <c r="E63">
-        <v>-19.15382593545847</v>
+        <v>-17.03048334342394</v>
       </c>
       <c r="F63">
-        <v>0.5940287442392401</v>
+        <v>1.203220901034233</v>
       </c>
       <c r="G63">
-        <v>-10.68387978918833</v>
+        <v>-8.54155624926962</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.618305474883435</v>
       </c>
       <c r="E64">
-        <v>-19.41202593795381</v>
+        <v>-16.26188809247208</v>
       </c>
       <c r="F64">
-        <v>0.4769779451214616</v>
+        <v>1.281147079350388</v>
       </c>
       <c r="G64">
-        <v>-10.60456904970401</v>
+        <v>-8.626756449268303</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.60753653164179</v>
       </c>
       <c r="E65">
-        <v>-19.17016014120414</v>
+        <v>-16.70508078665477</v>
       </c>
       <c r="F65">
-        <v>0.2617830044874004</v>
+        <v>0.9893977368192077</v>
       </c>
       <c r="G65">
-        <v>-10.39598812800223</v>
+        <v>-9.070829717360601</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.546826572035934</v>
       </c>
       <c r="E66">
-        <v>-18.08237087134763</v>
+        <v>-15.94583230605475</v>
       </c>
       <c r="F66">
-        <v>0.3717007318996724</v>
+        <v>1.088367760636082</v>
       </c>
       <c r="G66">
-        <v>-10.90026697727171</v>
+        <v>-9.135239691372661</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.434715776268375</v>
       </c>
       <c r="E67">
-        <v>-18.06424338989493</v>
+        <v>-16.43963975422116</v>
       </c>
       <c r="F67">
-        <v>0.06204208611996682</v>
+        <v>0.9671361912363738</v>
       </c>
       <c r="G67">
-        <v>-10.38291809421319</v>
+        <v>-8.228984471088252</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.264105355540977</v>
       </c>
       <c r="E68">
-        <v>-19.44564080051275</v>
+        <v>-15.49025423546109</v>
       </c>
       <c r="F68">
-        <v>-0.1125355156526262</v>
+        <v>0.8362193501631344</v>
       </c>
       <c r="G68">
-        <v>-10.1358289067986</v>
+        <v>-8.760555457783488</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.043980387455322</v>
       </c>
       <c r="E69">
-        <v>-18.02860882792857</v>
+        <v>-15.51705827311249</v>
       </c>
       <c r="F69">
-        <v>-0.2394687378858028</v>
+        <v>0.6773318553669668</v>
       </c>
       <c r="G69">
-        <v>-10.81430204125346</v>
+        <v>-8.304140475920788</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.77053168454535</v>
       </c>
       <c r="E70">
-        <v>-18.37526351321574</v>
+        <v>-14.46989394357879</v>
       </c>
       <c r="F70">
-        <v>-0.3337800234293322</v>
+        <v>0.3965782617405472</v>
       </c>
       <c r="G70">
-        <v>-10.26188785984297</v>
+        <v>-7.987308025630377</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.439473273177276</v>
       </c>
       <c r="E71">
-        <v>-18.30442006583974</v>
+        <v>-15.1883363448957</v>
       </c>
       <c r="F71">
-        <v>-0.5151552081092979</v>
+        <v>0.5640890611998576</v>
       </c>
       <c r="G71">
-        <v>-10.48246619857907</v>
+        <v>-8.128092285233423</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.055481279107656</v>
       </c>
       <c r="E72">
-        <v>-18.50147661228351</v>
+        <v>-15.10374897890642</v>
       </c>
       <c r="F72">
-        <v>-0.3890213604198228</v>
+        <v>0.4252397738774101</v>
       </c>
       <c r="G72">
-        <v>-10.3946539781499</v>
+        <v>-7.878768479579832</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.611330617621415</v>
       </c>
       <c r="E73">
-        <v>-18.12847526521972</v>
+        <v>-15.98660668601981</v>
       </c>
       <c r="F73">
-        <v>-0.5965953209481285</v>
+        <v>0.7422311279066969</v>
       </c>
       <c r="G73">
-        <v>-9.970732000755149</v>
+        <v>-8.645080318828169</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.105004046822476</v>
       </c>
       <c r="E74">
-        <v>-18.54820140709466</v>
+        <v>-15.67833534642166</v>
       </c>
       <c r="F74">
-        <v>-0.588441700602373</v>
+        <v>0.3725075617499991</v>
       </c>
       <c r="G74">
-        <v>-10.34583336308227</v>
+        <v>-7.814560448845667</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.53733998589734</v>
       </c>
       <c r="E75">
-        <v>-19.18230550849271</v>
+        <v>-15.45884021126988</v>
       </c>
       <c r="F75">
-        <v>-0.2988262325008042</v>
+        <v>0.2653665218719111</v>
       </c>
       <c r="G75">
-        <v>-9.466453151485664</v>
+        <v>-7.917538278390237</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.901441195282987</v>
       </c>
       <c r="E76">
-        <v>-18.6102143301557</v>
+        <v>-15.94210990042044</v>
       </c>
       <c r="F76">
-        <v>-0.6414290498898462</v>
+        <v>0.2559529547064975</v>
       </c>
       <c r="G76">
-        <v>-10.07109780986923</v>
+        <v>-7.398361974194033</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.201513061687026</v>
       </c>
       <c r="E77">
-        <v>-18.80639235264198</v>
+        <v>-16.38615394771657</v>
       </c>
       <c r="F77">
-        <v>-0.736704555090234</v>
+        <v>0.1117706380448267</v>
       </c>
       <c r="G77">
-        <v>-9.507616474720963</v>
+        <v>-7.504173630720219</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.439988590109915</v>
       </c>
       <c r="E78">
-        <v>-19.28503846983072</v>
+        <v>-17.03472199509511</v>
       </c>
       <c r="F78">
-        <v>-0.8026285181072271</v>
+        <v>-0.05316559552658282</v>
       </c>
       <c r="G78">
-        <v>-9.509076425303782</v>
+        <v>-7.189632077942985</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.616508606408983</v>
       </c>
       <c r="E79">
-        <v>-20.01093473936425</v>
+        <v>-17.29268198846805</v>
       </c>
       <c r="F79">
-        <v>-0.9886450453450785</v>
+        <v>-0.3443309390387895</v>
       </c>
       <c r="G79">
-        <v>-9.063040003706696</v>
+        <v>-6.882400209716462</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.744506661209212</v>
       </c>
       <c r="E80">
-        <v>-20.09756444713098</v>
+        <v>-17.86688343569264</v>
       </c>
       <c r="F80">
-        <v>-0.8564881382698482</v>
+        <v>-0.1152749266536841</v>
       </c>
       <c r="G80">
-        <v>-8.979514939750883</v>
+        <v>-6.667658362766097</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.832480050691264</v>
       </c>
       <c r="E81">
-        <v>-20.73881448051313</v>
+        <v>-16.77092027025229</v>
       </c>
       <c r="F81">
-        <v>-0.9547822142860375</v>
+        <v>0.00296126621750048</v>
       </c>
       <c r="G81">
-        <v>-8.119269681371266</v>
+        <v>-6.786900902545105</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.8901689711287113</v>
       </c>
       <c r="E82">
-        <v>-21.13092598788929</v>
+        <v>-17.77114696669648</v>
       </c>
       <c r="F82">
-        <v>-0.898015852906993</v>
+        <v>-0.2424276662486027</v>
       </c>
       <c r="G82">
-        <v>-8.353096823355528</v>
+        <v>-6.038946038312027</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.0601450708904458</v>
       </c>
       <c r="E83">
-        <v>-22.14475622025252</v>
+        <v>-19.82618205679931</v>
       </c>
       <c r="F83">
-        <v>-1.013763630100168</v>
+        <v>-0.3602364215399427</v>
       </c>
       <c r="G83">
-        <v>-8.250764550191118</v>
+        <v>-6.256859387889014</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.005192330665564</v>
       </c>
       <c r="E84">
-        <v>-23.02798979070855</v>
+        <v>-20.29290923039985</v>
       </c>
       <c r="F84">
-        <v>-1.46892003997719</v>
+        <v>-0.1504780561704547</v>
       </c>
       <c r="G84">
-        <v>-8.208978844394437</v>
+        <v>-5.50007198815716</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.929842281355862</v>
       </c>
       <c r="E85">
-        <v>-23.09205411249506</v>
+        <v>-20.61534110821999</v>
       </c>
       <c r="F85">
-        <v>-1.279178344528949</v>
+        <v>-0.2950389367352049</v>
       </c>
       <c r="G85">
-        <v>-8.136070699983067</v>
+        <v>-6.012481537271093</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.813234943297593</v>
       </c>
       <c r="E86">
-        <v>-24.71355121499957</v>
+        <v>-21.95168020246149</v>
       </c>
       <c r="F86">
-        <v>-1.329471014655115</v>
+        <v>-0.1041632063125316</v>
       </c>
       <c r="G86">
-        <v>-8.144525833290366</v>
+        <v>-5.553298939337561</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.64466565460949</v>
       </c>
       <c r="E87">
-        <v>-25.00188368354194</v>
+        <v>-23.76189240228764</v>
       </c>
       <c r="F87">
-        <v>-1.34806951958277</v>
+        <v>-0.5452779603446991</v>
       </c>
       <c r="G87">
-        <v>-7.67755021115739</v>
+        <v>-5.585507236889131</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.4102239435465</v>
       </c>
       <c r="E88">
-        <v>-25.64230047770669</v>
+        <v>-23.72088707014818</v>
       </c>
       <c r="F88">
-        <v>-1.653720523867731</v>
+        <v>-0.5382666586474041</v>
       </c>
       <c r="G88">
-        <v>-7.902375979820375</v>
+        <v>-5.427206880837801</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.094389535135468</v>
       </c>
       <c r="E89">
-        <v>-27.4847871117855</v>
+        <v>-25.68683349109812</v>
       </c>
       <c r="F89">
-        <v>-1.764020128652694</v>
+        <v>-0.4412797463928324</v>
       </c>
       <c r="G89">
-        <v>-7.767560633824634</v>
+        <v>-5.779783291315721</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.688419180231106</v>
       </c>
       <c r="E90">
-        <v>-28.3701898212912</v>
+        <v>-25.84694674658732</v>
       </c>
       <c r="F90">
-        <v>-1.583807971806259</v>
+        <v>-0.8722337458622612</v>
       </c>
       <c r="G90">
-        <v>-7.827090863711809</v>
+        <v>-5.310407523666774</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>6.178196040420358</v>
       </c>
       <c r="E91">
-        <v>-30.27972277729058</v>
+        <v>-27.94637446738734</v>
       </c>
       <c r="F91">
-        <v>-1.863070504107639</v>
+        <v>-0.7907986032278473</v>
       </c>
       <c r="G91">
-        <v>-7.817675672198122</v>
+        <v>-4.727178784376751</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>6.552358844095745</v>
       </c>
       <c r="E92">
-        <v>-31.16044530890936</v>
+        <v>-29.65063396085603</v>
       </c>
       <c r="F92">
-        <v>-1.83729502400213</v>
+        <v>-0.7236561117613363</v>
       </c>
       <c r="G92">
-        <v>-7.886495292868491</v>
+        <v>-5.799169845993693</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.801803265208341</v>
       </c>
       <c r="E93">
-        <v>-32.62148272766307</v>
+        <v>-31.87068211532436</v>
       </c>
       <c r="F93">
-        <v>-1.866382316984032</v>
+        <v>-1.229451449338895</v>
       </c>
       <c r="G93">
-        <v>-7.991621666468047</v>
+        <v>-5.653204582621687</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>6.913881992391271</v>
       </c>
       <c r="E94">
-        <v>-34.53320293660816</v>
+        <v>-31.95730729461708</v>
       </c>
       <c r="F94">
-        <v>-1.999920112519729</v>
+        <v>-1.458355042121885</v>
       </c>
       <c r="G94">
-        <v>-8.217169134058594</v>
+        <v>-6.158191888636575</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>6.88728102572636</v>
       </c>
       <c r="E95">
-        <v>-36.78577459139957</v>
+        <v>-33.66092148053968</v>
       </c>
       <c r="F95">
-        <v>-2.239560175210404</v>
+        <v>-1.313785049515704</v>
       </c>
       <c r="G95">
-        <v>-7.899333588469784</v>
+        <v>-5.702286730786922</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>6.709367564860659</v>
       </c>
       <c r="E96">
-        <v>-37.52565026019478</v>
+        <v>-36.44253211127719</v>
       </c>
       <c r="F96">
-        <v>-2.277143204275417</v>
+        <v>-1.5682263809596</v>
       </c>
       <c r="G96">
-        <v>-8.528211440200819</v>
+        <v>-6.101495485731017</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.3913775049393</v>
       </c>
       <c r="E97">
-        <v>-39.6391864417657</v>
+        <v>-38.05740179207146</v>
       </c>
       <c r="F97">
-        <v>-2.405011653306354</v>
+        <v>-1.433820456385769</v>
       </c>
       <c r="G97">
-        <v>-8.536203097132619</v>
+        <v>-6.278924173908256</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.914935014226208</v>
       </c>
       <c r="E98">
-        <v>-41.75087274170448</v>
+        <v>-39.86376478899109</v>
       </c>
       <c r="F98">
-        <v>-2.432944202128754</v>
+        <v>-1.801193115853322</v>
       </c>
       <c r="G98">
-        <v>-9.059093833423885</v>
+        <v>-6.589847300411066</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.325473228030773</v>
       </c>
       <c r="E99">
-        <v>-43.55663345158109</v>
+        <v>-41.73896964777533</v>
       </c>
       <c r="F99">
-        <v>-2.755925480847684</v>
+        <v>-1.963537387821372</v>
       </c>
       <c r="G99">
-        <v>-9.191873193912974</v>
+        <v>-6.815712580373383</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.56901305998224</v>
       </c>
       <c r="E100">
-        <v>-45.88322754250189</v>
+        <v>-44.14504298600475</v>
       </c>
       <c r="F100">
-        <v>-2.653874758659799</v>
+        <v>-2.289499132455575</v>
       </c>
       <c r="G100">
-        <v>-8.922914542665964</v>
+        <v>-7.522421357732681</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.763265328653335</v>
       </c>
       <c r="E101">
-        <v>-47.83183670071346</v>
+        <v>-46.12730097033031</v>
       </c>
       <c r="F101">
-        <v>-2.907957407018283</v>
+        <v>-2.209906278924987</v>
       </c>
       <c r="G101">
-        <v>-9.601496925123616</v>
+        <v>-7.056750090542178</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.749806528797134</v>
       </c>
       <c r="E102">
-        <v>-49.82395770142773</v>
+        <v>-48.02086652697864</v>
       </c>
       <c r="F102">
-        <v>-3.114738619942109</v>
+        <v>-2.819895325161473</v>
       </c>
       <c r="G102">
-        <v>-9.872137333504574</v>
+        <v>-7.677536968975233</v>
       </c>
     </row>
   </sheetData>
